--- a/Capitulo999_INSTITUTO/Taller1_2026/PlanillasDeControl_Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/PlanillasDeControl_Taller01_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="70">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>Registrada</t>
+  </si>
+  <si>
+    <t>23.09.2026</t>
+  </si>
+  <si>
+    <t>CONTROL FUNCIONES</t>
   </si>
 </sst>
 </file>
@@ -590,14 +596,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="B2:I103"/>
+  <dimension ref="B2:I109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.28515625" bestFit="1" customWidth="1"/>
@@ -635,7 +640,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>67</v>
       </c>
@@ -652,7 +657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>67</v>
       </c>
@@ -669,7 +674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>67</v>
       </c>
@@ -686,7 +691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>67</v>
       </c>
@@ -720,7 +725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>67</v>
       </c>
@@ -737,7 +742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>67</v>
       </c>
@@ -757,7 +762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>67</v>
       </c>
@@ -774,7 +779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>67</v>
       </c>
@@ -791,7 +796,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>67</v>
       </c>
@@ -808,7 +813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>67</v>
       </c>
@@ -825,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>67</v>
       </c>
@@ -842,7 +847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>67</v>
       </c>
@@ -862,7 +867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>67</v>
       </c>
@@ -902,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>67</v>
       </c>
@@ -919,7 +924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>67</v>
       </c>
@@ -939,7 +944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>67</v>
       </c>
@@ -959,7 +964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -982,7 +987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>67</v>
       </c>
@@ -1002,7 +1007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>67</v>
       </c>
@@ -1016,7 +1021,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>67</v>
       </c>
@@ -1030,7 +1035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>67</v>
       </c>
@@ -1047,7 +1052,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>67</v>
       </c>
@@ -1064,7 +1069,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>67</v>
       </c>
@@ -1081,7 +1086,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>67</v>
       </c>
@@ -1092,7 +1097,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>67</v>
       </c>
@@ -1103,7 +1108,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>67</v>
       </c>
@@ -1114,7 +1119,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>67</v>
       </c>
@@ -1122,7 +1127,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>67</v>
       </c>
@@ -1133,7 +1138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>67</v>
       </c>
@@ -1141,7 +1146,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>67</v>
       </c>
@@ -1149,7 +1154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>67</v>
       </c>
@@ -1157,7 +1162,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -1165,7 +1170,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>67</v>
       </c>
@@ -1173,7 +1178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>67</v>
       </c>
@@ -1184,7 +1189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>67</v>
       </c>
@@ -1201,7 +1206,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>67</v>
       </c>
@@ -1218,7 +1223,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>67</v>
       </c>
@@ -1226,7 +1231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>67</v>
       </c>
@@ -1237,7 +1242,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>67</v>
       </c>
@@ -1251,7 +1256,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>67</v>
       </c>
@@ -1262,7 +1267,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>67</v>
       </c>
@@ -1273,7 +1278,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>39</v>
       </c>
@@ -1287,7 +1292,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -1304,7 +1309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>67</v>
       </c>
@@ -1321,7 +1326,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>67</v>
       </c>
@@ -1338,7 +1343,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>67</v>
       </c>
@@ -1355,7 +1360,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>39</v>
       </c>
@@ -1369,7 +1374,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>67</v>
       </c>
@@ -1386,7 +1391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>67</v>
       </c>
@@ -1403,7 +1408,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>67</v>
       </c>
@@ -1420,7 +1425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>67</v>
       </c>
@@ -1434,7 +1439,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>67</v>
       </c>
@@ -1448,7 +1453,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>67</v>
       </c>
@@ -1462,7 +1467,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>67</v>
       </c>
@@ -1476,7 +1481,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>67</v>
       </c>
@@ -1493,7 +1498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>67</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>67</v>
       </c>
@@ -1524,7 +1529,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>67</v>
       </c>
@@ -1538,7 +1543,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>67</v>
       </c>
@@ -1569,7 +1574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>67</v>
       </c>
@@ -1583,7 +1588,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>67</v>
       </c>
@@ -1597,7 +1602,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>67</v>
       </c>
@@ -1611,7 +1616,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>67</v>
       </c>
@@ -1628,7 +1633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>67</v>
       </c>
@@ -1645,7 +1650,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>56</v>
       </c>
@@ -1659,7 +1664,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>67</v>
       </c>
@@ -1679,7 +1684,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>67</v>
       </c>
@@ -1699,7 +1704,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>67</v>
       </c>
@@ -1720,7 +1725,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>67</v>
       </c>
@@ -1741,7 +1746,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>45</v>
       </c>
@@ -1755,7 +1760,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>67</v>
       </c>
@@ -1776,7 +1781,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>67</v>
       </c>
@@ -1796,7 +1801,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>67</v>
       </c>
@@ -1816,7 +1821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="80" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>67</v>
       </c>
@@ -1836,7 +1841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>67</v>
       </c>
@@ -1856,7 +1861,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="82" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>67</v>
       </c>
@@ -1876,7 +1881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>67</v>
       </c>
@@ -1896,7 +1901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>67</v>
       </c>
@@ -1916,7 +1921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>67</v>
       </c>
@@ -1936,7 +1941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>67</v>
       </c>
@@ -1954,7 +1959,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>67</v>
       </c>
@@ -1974,7 +1979,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>67</v>
       </c>
@@ -2011,7 +2016,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="90" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>67</v>
       </c>
@@ -2028,7 +2033,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="91" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>67</v>
       </c>
@@ -2045,7 +2050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="92" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>67</v>
       </c>
@@ -2065,7 +2070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="93" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>67</v>
       </c>
@@ -2085,7 +2090,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>67</v>
       </c>
@@ -2105,7 +2110,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>67</v>
       </c>
@@ -2128,7 +2133,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>67</v>
       </c>
@@ -2151,7 +2156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="97" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>67</v>
       </c>
@@ -2174,7 +2179,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="98" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>39</v>
       </c>
@@ -2194,7 +2199,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="99" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>67</v>
       </c>
@@ -2217,7 +2222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>67</v>
       </c>
@@ -2237,7 +2242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>67</v>
       </c>
@@ -2260,7 +2265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="102" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>39</v>
       </c>
@@ -2280,7 +2285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>67</v>
       </c>
@@ -2300,14 +2305,104 @@
         <v>66</v>
       </c>
     </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>41</v>
+      </c>
+      <c r="D104" t="s">
+        <v>68</v>
+      </c>
+      <c r="E104" t="s">
+        <v>69</v>
+      </c>
+      <c r="G104" t="s">
+        <v>62</v>
+      </c>
+      <c r="H104" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>68</v>
+      </c>
+      <c r="E105" t="s">
+        <v>69</v>
+      </c>
+      <c r="G105" t="s">
+        <v>62</v>
+      </c>
+      <c r="H105" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>68</v>
+      </c>
+      <c r="E106" t="s">
+        <v>69</v>
+      </c>
+      <c r="G106" t="s">
+        <v>62</v>
+      </c>
+      <c r="H106" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>68</v>
+      </c>
+      <c r="E107" t="s">
+        <v>69</v>
+      </c>
+      <c r="G107" t="s">
+        <v>62</v>
+      </c>
+      <c r="H107" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" t="s">
+        <v>69</v>
+      </c>
+      <c r="G108" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" t="s">
+        <v>69</v>
+      </c>
+      <c r="G109" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B3:G103">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="VERON NIEVA, Maximo Joaquin"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B3:G103"/>
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>

--- a/Capitulo999_INSTITUTO/Taller1_2026/PlanillasDeControl_Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/PlanillasDeControl_Taller01_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="72">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>CONTROL FUNCIONES</t>
+  </si>
+  <si>
+    <t>EXE</t>
+  </si>
+  <si>
+    <t>14.10.2026</t>
   </si>
 </sst>
 </file>
@@ -596,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I109"/>
+  <dimension ref="B2:I127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -2401,6 +2407,204 @@
         <v>62</v>
       </c>
     </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>39</v>
+      </c>
+      <c r="C110" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>39</v>
+      </c>
+      <c r="C111" t="s">
+        <v>47</v>
+      </c>
+      <c r="D111" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>70</v>
+      </c>
+      <c r="C112" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" t="s">
+        <v>71</v>
+      </c>
+      <c r="G112" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>70</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>39</v>
+      </c>
+      <c r="C114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>70</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>70</v>
+      </c>
+      <c r="C116" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>70</v>
+      </c>
+      <c r="C117" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" t="s">
+        <v>71</v>
+      </c>
+      <c r="E117" t="s">
+        <v>59</v>
+      </c>
+      <c r="G117" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>39</v>
+      </c>
+      <c r="C118" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>39</v>
+      </c>
+      <c r="C119" t="s">
+        <v>37</v>
+      </c>
+      <c r="D119" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>39</v>
+      </c>
+      <c r="C120" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>70</v>
+      </c>
+      <c r="C121" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>70</v>
+      </c>
+      <c r="C122" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" t="s">
+        <v>56</v>
+      </c>
+      <c r="D123" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>70</v>
+      </c>
+      <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C126" t="s">
+        <v>40</v>
+      </c>
+      <c r="D126" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B3:G103"/>
   <mergeCells count="1">
